--- a/Grafik_CCEE_SLIVEN1_05_08_2026.xlsx
+++ b/Grafik_CCEE_SLIVEN1_05_08_2026.xlsx
@@ -1827,8 +1827,10 @@
       <c r="B58" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C58" s="11" t="n">
-        <v>0</v>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D58" s="5" t="n">
         <v>0</v>
@@ -2147,10 +2149,8 @@
       <c r="B74" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C74" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D74" s="5" t="n">
         <v>0</v>
@@ -2323,13 +2323,11 @@
       <c r="B82" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C82" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E82" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C82+D82,0))),MIN(1800,MAX(0,D82)))</f>
@@ -2345,13 +2343,11 @@
       <c r="B83" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C83" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C83" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E83" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C83+D83,0))),MIN(1800,MAX(0,D83)))</f>
@@ -2367,13 +2363,11 @@
       <c r="B84" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C84" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E84" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C84+D84,0))),MIN(1800,MAX(0,D84)))</f>
@@ -2489,11 +2483,13 @@
       <c r="B90" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C90" s="11" t="n">
-        <v>0</v>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D90" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E90" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C90+D90,0))),MIN(1800,MAX(0,D90)))</f>
@@ -2509,11 +2505,13 @@
       <c r="B91" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C91" s="11" t="n">
-        <v>0</v>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D91" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E91" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C91+D91,0))),MIN(1800,MAX(0,D91)))</f>
@@ -2529,11 +2527,13 @@
       <c r="B92" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C92" s="11" t="n">
-        <v>0</v>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D92" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="E92" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C92+D92,0))),MIN(1800,MAX(0,D92)))</f>

--- a/Grafik_CCEE_SLIVEN1_05_08_2026.xlsx
+++ b/Grafik_CCEE_SLIVEN1_05_08_2026.xlsx
@@ -1827,10 +1827,8 @@
       <c r="B58" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C58" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D58" s="5" t="n">
         <v>0</v>
@@ -2149,8 +2147,10 @@
       <c r="B74" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C74" s="11" t="n">
-        <v>0</v>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>Put Adex Solcast value here</t>
+        </is>
       </c>
       <c r="D74" s="5" t="n">
         <v>0</v>
@@ -2483,13 +2483,11 @@
       <c r="B90" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C90" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C90" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E90" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C90+D90,0))),MIN(1800,MAX(0,D90)))</f>
@@ -2505,13 +2503,11 @@
       <c r="B91" s="1" t="n">
         <v>46239</v>
       </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>Put Adex Solcast value here</t>
-        </is>
+      <c r="C91" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E91" s="9">
         <f>IFERROR(MIN(1800,MAX(0,ROUND(C91+D91,0))),MIN(1800,MAX(0,D91)))</f>
